--- a/backend/data/uploads/MES/2026-07-07_불량현황.xlsx
+++ b/backend/data/uploads/MES/2026-07-07_불량현황.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sihoo\PythonProject\TestProject\backend\data\uploads\MES\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{C0649F06-1D12-4101-ABB0-3EA5BF6D4141}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{540F9E0A-E2E6-4C24-9D31-70729C4A4127}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-30828" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{B9447A1B-4A9E-4466-A198-3C438E1DFDBC}"/>
+    <workbookView xWindow="-30828" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{7116B144-FD3E-4321-97CF-425A6420B16A}"/>
   </bookViews>
   <sheets>
     <sheet name="불량현황" sheetId="1" r:id="rId1"/>
@@ -492,7 +492,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AFA9FC63-CED8-40CB-B2F8-151CB387977F}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3596C3FB-BACF-4EF2-A9B7-42327748FB93}">
   <dimension ref="B2:U12"/>
   <sheetFormatPr defaultRowHeight="17.600000000000001" x14ac:dyDescent="0.55000000000000004"/>
   <cols>

--- a/backend/data/uploads/MES/2026-07-07_불량현황.xlsx
+++ b/backend/data/uploads/MES/2026-07-07_불량현황.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sihoo\PythonProject\TestProject\backend\data\uploads\MES\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{540F9E0A-E2E6-4C24-9D31-70729C4A4127}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{D11109D8-02F3-449C-B2EB-7D7F01EFAA95}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-30828" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{7116B144-FD3E-4321-97CF-425A6420B16A}"/>
+    <workbookView xWindow="-30828" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{D1E822C4-13DC-457F-8726-5BB8253ACE28}"/>
   </bookViews>
   <sheets>
     <sheet name="불량현황" sheetId="1" r:id="rId1"/>
@@ -492,7 +492,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3596C3FB-BACF-4EF2-A9B7-42327748FB93}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00CE869C-2F6D-4BBD-9BD0-9AC3B9AFC09B}">
   <dimension ref="B2:U12"/>
   <sheetFormatPr defaultRowHeight="17.600000000000001" x14ac:dyDescent="0.55000000000000004"/>
   <cols>

--- a/backend/data/uploads/MES/2026-07-07_불량현황.xlsx
+++ b/backend/data/uploads/MES/2026-07-07_불량현황.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sihoo\PythonProject\TestProject\backend\data\uploads\MES\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{D11109D8-02F3-449C-B2EB-7D7F01EFAA95}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{66BAE1F4-928A-43EC-8FBD-0649B6C088EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-30828" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{D1E822C4-13DC-457F-8726-5BB8253ACE28}"/>
+    <workbookView xWindow="-30240" yWindow="8376" windowWidth="23040" windowHeight="12012" xr2:uid="{AAEB0CEF-E941-4C90-BF5D-B505A7B57440}"/>
   </bookViews>
   <sheets>
     <sheet name="불량현황" sheetId="1" r:id="rId1"/>
@@ -492,7 +492,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00CE869C-2F6D-4BBD-9BD0-9AC3B9AFC09B}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3315EA9D-0F38-4EB3-B3CC-6E9C0D201AD1}">
   <dimension ref="B2:U12"/>
   <sheetFormatPr defaultRowHeight="17.600000000000001" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
